--- a/erwinmodels/3_final/reports/03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated_V3_Final_Fidelity_Report.xlsx
+++ b/erwinmodels/3_final/reports/03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated_V3_Final_Fidelity_Report.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="V3_OVERVIEW" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SUMMARY" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="DASHBOARD" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="FINDINGS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ENTITY_MATRIX" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="RELATIONSHIPS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CATEGORY_ANALYSIS" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="DESCRIPTION" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="CONFIG" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="03_Lubes_Sales_Marketing_Ind" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="UDP_MAPPING_SUMMARY" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="UDP_DEFINITIONS" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="UDP_VALUE_RECON" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="UDP_EXCEPTIONS" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V3_OVERVIEW" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINDINGS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENTITY_MATRIX" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RELATIONSHIPS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATEGORY_ANALYSIS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DESCRIPTION" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Lubes_Sales_Marketing_Ind" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UDP_MAPPING_SUMMARY" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UDP_DEFINITIONS" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UDP_VALUE_RECON" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UDP_EXCEPTIONS" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SUMMARY'!$A$2:$AH$3</definedName>
@@ -426,13 +426,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -451,7 +451,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -491,8 +491,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -515,7 +515,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>10</col>
@@ -530,9 +530,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="B4" s="33" t="inlineStr">
         <is>
-          <t>2026-09-04 19:46:54</t>
+          <t>2026-09-05 21:16:23</t>
         </is>
       </c>
       <c r="C4" s="25" t="n"/>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>C:\Users\Shivansh\Downloads\migration-platform_4_sept_final\sappdmodels\ldm\03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated.ldm</t>
+          <t>C:\Users\SrinivasaPesala\Desktop\migration-platform_4_sept_final_h_l_m\sappdmodels\ldm\03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated.ldm</t>
         </is>
       </c>
       <c r="C6" s="25" t="inlineStr">
@@ -11361,7 +11361,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SAP PD (PowerDesigner LDM) -&gt; erwin  |  Logical Model Validation Report   |   generated 2026-09-04 19:47</t>
+          <t>SAP PD (PowerDesigner LDM) -&gt; erwin  |  Logical Model Validation Report   |   generated 2026-09-05 21:17</t>
         </is>
       </c>
     </row>
@@ -48812,7 +48812,7 @@
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>{"CHAR": "{'CHAR'}", "VARCHAR": "{'VARCHAR'}", "TEXT": "{'TEXT', 'LONG_TEXT', 'CLOB', 'LONGTEXT'}", "INTEGER": "{'INTEGER'}", "SMALLINT": "{'SMALLINT'}", "BIGINT": "{'BIGINT'}", "DECIMAL": "{'DECIMAL'}", "DATE": "{'DATE'}", "TIME": "{'TIME'}", "TIMESTAMP": "{'TIMESTAMP'}", "BINARY": "{'BINARY'}", "VARBINARY": "{'VARBINARY'}", "BOOLEAN": "{'BOOLEAN', 'BIT', 'BOOL'}", "XML": "{'XML'}"}</t>
+          <t>{"CHAR": "{'CHAR'}", "VARCHAR": "{'VARCHAR'}", "TEXT": "{'LONGTEXT', 'CLOB', 'TEXT', 'LONG_TEXT'}", "INTEGER": "{'INTEGER'}", "SMALLINT": "{'SMALLINT'}", "BIGINT": "{'BIGINT'}", "DECIMAL": "{'DECIMAL'}", "DATE": "{'DATE'}", "TIME": "{'TIME'}", "TIMESTAMP": "{'TIMESTAMP'}", "BINARY": "{'BINARY'}", "VARBINARY": "{'VARBINARY'}", "BOOLEAN": "{'BIT', 'BOOL', 'BOOLEAN'}", "XML": "{'XML'}"}</t>
         </is>
       </c>
     </row>

--- a/erwinmodels/3_final/reports/03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated_V3_Final_Fidelity_Report.xlsx
+++ b/erwinmodels/3_final/reports/03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated_V3_Final_Fidelity_Report.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V3_OVERVIEW" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUMMARY" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FINDINGS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENTITY_MATRIX" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RELATIONSHIPS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATEGORY_ANALYSIS" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DESCRIPTION" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Lubes_Sales_Marketing_Ind" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UDP_MAPPING_SUMMARY" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UDP_DEFINITIONS" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UDP_VALUE_RECON" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UDP_EXCEPTIONS" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="V3_OVERVIEW" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SUMMARY" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="DASHBOARD" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="FINDINGS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ENTITY_MATRIX" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="RELATIONSHIPS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CATEGORY_ANALYSIS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="DESCRIPTION" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="CONFIG" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="03_Lubes_Sales_Marketing_Ind" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="UDP_MAPPING_SUMMARY" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="UDP_DEFINITIONS" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="UDP_VALUE_RECON" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="UDP_EXCEPTIONS" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SUMMARY'!$A$2:$AH$3</definedName>
@@ -426,13 +426,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -451,7 +451,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -491,8 +491,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -515,7 +515,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>10</col>
@@ -530,9 +530,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="B4" s="33" t="inlineStr">
         <is>
-          <t>2026-09-05 21:16:23</t>
+          <t>2026-09-05 20:21:02</t>
         </is>
       </c>
       <c r="C4" s="25" t="n"/>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>C:\Users\SrinivasaPesala\Desktop\migration-platform_4_sept_final_h_l_m\sappdmodels\ldm\03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated.ldm</t>
+          <t>C:\Users\Shivansh\Downloads\migration-platform_4_sept_final\sappdmodels\ldm\03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated.ldm</t>
         </is>
       </c>
       <c r="C6" s="25" t="inlineStr">
@@ -11361,7 +11361,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SAP PD (PowerDesigner LDM) -&gt; erwin  |  Logical Model Validation Report   |   generated 2026-09-05 21:17</t>
+          <t>SAP PD (PowerDesigner LDM) -&gt; erwin  |  Logical Model Validation Report   |   generated 2026-09-05 20:24</t>
         </is>
       </c>
     </row>
@@ -48812,7 +48812,7 @@
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>{"CHAR": "{'CHAR'}", "VARCHAR": "{'VARCHAR'}", "TEXT": "{'LONGTEXT', 'CLOB', 'TEXT', 'LONG_TEXT'}", "INTEGER": "{'INTEGER'}", "SMALLINT": "{'SMALLINT'}", "BIGINT": "{'BIGINT'}", "DECIMAL": "{'DECIMAL'}", "DATE": "{'DATE'}", "TIME": "{'TIME'}", "TIMESTAMP": "{'TIMESTAMP'}", "BINARY": "{'BINARY'}", "VARBINARY": "{'VARBINARY'}", "BOOLEAN": "{'BIT', 'BOOL', 'BOOLEAN'}", "XML": "{'XML'}"}</t>
+          <t>{"CHAR": "{'CHAR'}", "VARCHAR": "{'VARCHAR'}", "TEXT": "{'CLOB', 'LONGTEXT', 'TEXT', 'LONG_TEXT'}", "INTEGER": "{'INTEGER'}", "SMALLINT": "{'SMALLINT'}", "BIGINT": "{'BIGINT'}", "DECIMAL": "{'DECIMAL'}", "DATE": "{'DATE'}", "TIME": "{'TIME'}", "TIMESTAMP": "{'TIMESTAMP'}", "BINARY": "{'BINARY'}", "VARBINARY": "{'VARBINARY'}", "BOOLEAN": "{'BOOLEAN', 'BOOL', 'BIT'}", "XML": "{'XML'}"}</t>
         </is>
       </c>
     </row>
